--- a/static/files/DMAX-2024-Live - Copy.xlsx
+++ b/static/files/DMAX-2024-Live - Copy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD40F509-3C0E-45CA-B457-4879668310CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CE83A9-90D6-4C87-933D-2285599F5C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>Basic Information</t>
   </si>
@@ -331,19 +331,19 @@
     <t>Blank</t>
   </si>
   <si>
-    <t>Sathya S</t>
+    <t>Tanushree</t>
   </si>
   <si>
-    <t>sathya@qaoncloud.com</t>
+    <t>DC4771</t>
   </si>
   <si>
-    <t>LevelBlue</t>
+    <t>Indihood</t>
   </si>
   <si>
-    <t>SrQAEngineer</t>
+    <t>QALead</t>
   </si>
   <si>
-    <t>DC1531</t>
+    <t>Suganya@qaoncloud.com</t>
   </si>
 </sst>
 </file>
@@ -774,6 +774,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -936,7 +937,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1206,201 +1206,201 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="23.4" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="48" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="63" t="s">
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="64"/>
-      <c r="AK1" s="64"/>
-      <c r="AL1" s="64"/>
-      <c r="AM1" s="64"/>
-      <c r="AN1" s="64"/>
-      <c r="AO1" s="64"/>
-      <c r="AP1" s="64"/>
-      <c r="AQ1" s="64"/>
-      <c r="AR1" s="65"/>
-      <c r="AS1" s="69" t="s">
+      <c r="AJ1" s="65"/>
+      <c r="AK1" s="65"/>
+      <c r="AL1" s="65"/>
+      <c r="AM1" s="65"/>
+      <c r="AN1" s="65"/>
+      <c r="AO1" s="65"/>
+      <c r="AP1" s="65"/>
+      <c r="AQ1" s="65"/>
+      <c r="AR1" s="66"/>
+      <c r="AS1" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="AT1" s="70"/>
-      <c r="AU1" s="70"/>
-      <c r="AV1" s="70"/>
-      <c r="AW1" s="70"/>
-      <c r="AX1" s="70"/>
-      <c r="AY1" s="70"/>
-      <c r="AZ1" s="70"/>
-      <c r="BA1" s="70"/>
-      <c r="BB1" s="70"/>
-      <c r="BC1" s="70"/>
-      <c r="BD1" s="71"/>
-      <c r="BE1" s="75" t="s">
+      <c r="AT1" s="71"/>
+      <c r="AU1" s="71"/>
+      <c r="AV1" s="71"/>
+      <c r="AW1" s="71"/>
+      <c r="AX1" s="71"/>
+      <c r="AY1" s="71"/>
+      <c r="AZ1" s="71"/>
+      <c r="BA1" s="71"/>
+      <c r="BB1" s="71"/>
+      <c r="BC1" s="71"/>
+      <c r="BD1" s="72"/>
+      <c r="BE1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="BF1" s="76"/>
-      <c r="BG1" s="76"/>
-      <c r="BH1" s="77"/>
-      <c r="BI1" s="81" t="s">
+      <c r="BF1" s="77"/>
+      <c r="BG1" s="77"/>
+      <c r="BH1" s="78"/>
+      <c r="BI1" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="BJ1" s="82"/>
-      <c r="BK1" s="83"/>
-      <c r="BL1" s="51" t="s">
+      <c r="BJ1" s="83"/>
+      <c r="BK1" s="84"/>
+      <c r="BL1" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="BM1" s="52"/>
-      <c r="BN1" s="53"/>
-      <c r="BO1" s="42" t="s">
+      <c r="BM1" s="53"/>
+      <c r="BN1" s="54"/>
+      <c r="BO1" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="42" t="s">
+      <c r="BP1" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="BQ1" s="42" t="s">
+      <c r="BQ1" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="BR1" s="44" t="s">
+      <c r="BR1" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="BS1" s="46" t="s">
+      <c r="BS1" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="BT1" s="33" t="s">
+      <c r="BT1" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="BU1" s="34"/>
-      <c r="BV1" s="34"/>
-      <c r="BW1" s="34"/>
-      <c r="BX1" s="34"/>
-      <c r="BY1" s="35"/>
+      <c r="BU1" s="35"/>
+      <c r="BV1" s="35"/>
+      <c r="BW1" s="35"/>
+      <c r="BX1" s="35"/>
+      <c r="BY1" s="36"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1"/>
       <c r="CB1" s="1"/>
     </row>
     <row r="2" spans="1:80" ht="21" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="36" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="36" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="36" t="s">
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="39"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="36" t="s">
+      <c r="X2" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="67"/>
-      <c r="AK2" s="67"/>
-      <c r="AL2" s="67"/>
-      <c r="AM2" s="67"/>
-      <c r="AN2" s="67"/>
-      <c r="AO2" s="67"/>
-      <c r="AP2" s="67"/>
-      <c r="AQ2" s="67"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="72"/>
-      <c r="AT2" s="73"/>
-      <c r="AU2" s="73"/>
-      <c r="AV2" s="73"/>
-      <c r="AW2" s="73"/>
-      <c r="AX2" s="73"/>
-      <c r="AY2" s="73"/>
-      <c r="AZ2" s="73"/>
-      <c r="BA2" s="73"/>
-      <c r="BB2" s="73"/>
-      <c r="BC2" s="73"/>
-      <c r="BD2" s="74"/>
-      <c r="BE2" s="78"/>
-      <c r="BF2" s="79"/>
-      <c r="BG2" s="79"/>
-      <c r="BH2" s="80"/>
-      <c r="BI2" s="84"/>
-      <c r="BJ2" s="85"/>
-      <c r="BK2" s="86"/>
-      <c r="BL2" s="54"/>
-      <c r="BM2" s="55"/>
-      <c r="BN2" s="56"/>
-      <c r="BO2" s="43"/>
-      <c r="BP2" s="43"/>
-      <c r="BQ2" s="43"/>
-      <c r="BR2" s="45"/>
-      <c r="BS2" s="47"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="39"/>
+      <c r="AI2" s="67"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="69"/>
+      <c r="AS2" s="73"/>
+      <c r="AT2" s="74"/>
+      <c r="AU2" s="74"/>
+      <c r="AV2" s="74"/>
+      <c r="AW2" s="74"/>
+      <c r="AX2" s="74"/>
+      <c r="AY2" s="74"/>
+      <c r="AZ2" s="74"/>
+      <c r="BA2" s="74"/>
+      <c r="BB2" s="74"/>
+      <c r="BC2" s="74"/>
+      <c r="BD2" s="75"/>
+      <c r="BE2" s="79"/>
+      <c r="BF2" s="80"/>
+      <c r="BG2" s="80"/>
+      <c r="BH2" s="81"/>
+      <c r="BI2" s="85"/>
+      <c r="BJ2" s="86"/>
+      <c r="BK2" s="87"/>
+      <c r="BL2" s="55"/>
+      <c r="BM2" s="56"/>
+      <c r="BN2" s="57"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="46"/>
+      <c r="BS2" s="48"/>
       <c r="BT2" s="3"/>
       <c r="BU2" s="4"/>
       <c r="BV2" s="5"/>
-      <c r="BW2" s="39" t="s">
+      <c r="BW2" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="BX2" s="40"/>
-      <c r="BY2" s="41"/>
+      <c r="BX2" s="41"/>
+      <c r="BY2" s="42"/>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1"/>
       <c r="CB2" s="1"/>
@@ -1636,18 +1636,18 @@
         <v>88</v>
       </c>
       <c r="B4" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="31">
+        <v>45698</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="31">
-        <v>45349</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="87" t="s">
+      <c r="F4" s="33" t="s">
         <v>91</v>
       </c>
       <c r="G4" s="22">
@@ -1837,7 +1837,7 @@
    F4="QAEngineer", IFERROR(BM4/BL4*35/100, 0),
    F4="QALead", IFERROR(BM4/BL4*20/100, 0)
 )</f>
-        <v>3.7241379310344824E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="BO4" s="17" cm="1">
         <f t="array" ref="BO4">_xlfn.IFS(
@@ -1863,251 +1863,89 @@
       </c>
       <c r="BS4" s="17">
         <f t="shared" ref="BS4" si="2">SUM(BN4:BR4)</f>
-        <v>0.48724137931034484</v>
+        <v>0.47482758620689658</v>
       </c>
     </row>
     <row r="5" spans="1:80" ht="13.8">
-      <c r="A5" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="31">
-        <v>45350</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="87" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="22">
-        <v>60</v>
-      </c>
-      <c r="H5" s="22">
-        <v>5</v>
-      </c>
-      <c r="I5" s="20">
-        <v>80</v>
-      </c>
-      <c r="J5" s="20">
-        <v>11</v>
-      </c>
-      <c r="K5" s="20">
-        <v>100</v>
-      </c>
-      <c r="L5" s="22">
-        <v>0</v>
-      </c>
-      <c r="M5" s="22">
-        <v>5</v>
-      </c>
-      <c r="N5" s="22">
-        <v>0</v>
-      </c>
-      <c r="O5" s="22">
-        <v>10</v>
-      </c>
-      <c r="P5" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="22">
-        <v>100</v>
-      </c>
-      <c r="R5" s="22">
-        <v>0</v>
-      </c>
-      <c r="S5" s="20">
-        <v>20</v>
-      </c>
-      <c r="T5" s="20">
-        <v>0</v>
-      </c>
-      <c r="U5" s="20">
-        <v>200</v>
-      </c>
-      <c r="V5" s="22">
-        <v>0</v>
-      </c>
-      <c r="W5" s="20">
-        <v>5</v>
-      </c>
-      <c r="X5" s="22">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="22">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="22">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="22">
-        <v>20</v>
-      </c>
-      <c r="AB5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="20">
-        <v>10</v>
-      </c>
-      <c r="AD5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="20">
-        <v>100</v>
-      </c>
-      <c r="AF5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="20">
-        <v>400</v>
-      </c>
-      <c r="AH5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="20">
-        <v>10</v>
-      </c>
-      <c r="AJ5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="20">
-        <v>80</v>
-      </c>
-      <c r="AL5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="20">
-        <v>80</v>
-      </c>
-      <c r="AN5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="20">
-        <v>80</v>
-      </c>
-      <c r="AP5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="20">
-        <v>80</v>
-      </c>
-      <c r="AR5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="20">
-        <v>5</v>
-      </c>
-      <c r="AT5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="20">
-        <v>5</v>
-      </c>
-      <c r="AV5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="20">
-        <v>5</v>
-      </c>
-      <c r="AX5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AY5" s="20">
-        <v>5</v>
-      </c>
-      <c r="AZ5" s="20">
-        <v>3</v>
-      </c>
-      <c r="BA5" s="20">
-        <v>1</v>
-      </c>
-      <c r="BB5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BC5" s="20">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BE5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BF5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BG5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BH5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="19">
-        <v>1</v>
-      </c>
-      <c r="BJ5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BK5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BL5" s="23">
-        <f t="shared" ref="BL5" si="3">SUM(IF(H5&gt;0,G5),IF(J5&gt;0,I5),IF(L5&gt;0,K5),IF(N5&gt;0,M5),IF(P5&gt;0,O5),IF(R5&gt;0,Q5),IF(T5&gt;0,S5),IF(V5&gt;0,U5),IF(X5&gt;0,W5),IF(Z5&gt;0,Y5),IF(AB5&gt;0,AA5),IF(AD5&gt;0,AC5),IF(AF5&gt;0,AE5),IF(AH5&gt;0,AG5),IF(AJ5&gt;0,AI5),IF(AL5&gt;0,AK5),IF(AN5&gt;0,AM5),IF(AP5&gt;0,AO5),IF(AR5&gt;0,AQ5),IF(AT5&gt;0,AS5),IF(AV5&gt;0,AU5),IF(AX5&gt;0,AW5),IF(AZ5&gt;0,AY5),IF(BB5&gt;0,BA5),IF(BD5&gt;0,BC5))</f>
-        <v>145</v>
-      </c>
-      <c r="BM5" s="23">
-        <f t="shared" ref="BM5" si="4">SUM(H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5,AB5,AD5,AF5,AH5,AJ5,AL5,AN5,AP5,AR5,AT5,AV5,AX5,AZ5,BB5,BD5)</f>
-        <v>19</v>
-      </c>
-      <c r="BN5" s="17" cm="1">
-        <f t="array" ref="BN5">_xlfn.IFS(
-   F5="Intern", IFERROR(BM5/BL5*30/100, 0),
-   F5="SrQAEngineer", IFERROR(BM5/BL5*30/100, 0),
-   F5="JrQAEngineer", IFERROR(BM5/BL5*40/100, 0),
-   F5="QAEngineer", IFERROR(BM5/BL5*35/100, 0),
-   F5="QALead", IFERROR(BM5/BL5*20/100, 0)
-)</f>
-        <v>3.9310344827586212E-2</v>
-      </c>
-      <c r="BO5" s="17" cm="1">
-        <f t="array" ref="BO5">_xlfn.IFS(
-   F5="Intern", IF(AND(BG5=0, BI5&gt;=0.5, BL5&gt;0, BM5&gt;0), (100 - SUM(BE5:BH5)) * 0.5 / 100, 0),
-   F5="JrQAEngineer", IF(AND(BG5=0, BI5&gt;=0.5, BL5&gt;0, BM5&gt;0), (100 - SUM(BE5:BH5)) * 0.4 / 100, 0),
-   F5="QAEngineer", IF(AND(BG5=0, BI5&gt;=0.5, BL5&gt;0, BM5&gt;0), (100 - SUM(BE5:BH5)) * 0.4 / 100, 0),
-   F5="SrQAEngineer", IF(AND(BG5=0, BI5&gt;=0.5, BL5&gt;0, BM5&gt;0), (100 - SUM(BE5:BH5)) * 0.4 / 100, 0),
-   F5="QALead", IF(AND(BG5=0, BI5&gt;=0.5, BL5&gt;0, BM5&gt;0), (100 - SUM(BE5:BH5)) * 0.4 / 100, 0)
-)</f>
-        <v>0.4</v>
-      </c>
-      <c r="BP5" s="17" cm="1">
-        <f t="array" ref="BP5">_xlfn.IFS(F5="Intern", (BI5*1)*10/100, F5="JrQAEngineer", (BI5*1)*10/100, F5="QAEngineer", (BI5*1)*5/100, F5="SrQAEngineer", (BI5*1)*5/100, F5="QALead", (BI5*1)*5/100)</f>
-        <v>0.05</v>
-      </c>
-      <c r="BQ5" s="17" cm="1">
-        <f t="array" ref="BQ5">_xlfn.IFS(F5="Intern", IF(BI5&gt;=0.5, BJ5*10/100/100, 0), F5="JrQAEngineer", IF(BI5&gt;=0.5, BJ5*10/100/100, 0), F5="QAEngineer", IF(BI5&gt;=0.5, BJ5*5/100/100, 0), F5="SrQAEngineer", IF(BI5&gt;=0.5, BJ5*5/100/100, 0), F5="QALead", IF(BI5&gt;=0.5, BJ5*5/100/100, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="BR5" s="17" cm="1">
-        <f t="array" ref="BR5">_xlfn.IFS(F5="Intern", IF(BI5&gt;=0.5, BK5*0/100/100, 0), F5="JrQAEngineer", IF(BI5&gt;=0.5, BK5*0/100/100, 0), F5="QAEngineer", IF(BI5&gt;=0.5, BK5*15/100/100, 0), F5="SrQAEngineer", IF(BI5&gt;=0.5, BK5*20/100/100, 0), F5="QALead", IF(BI5&gt;=0.5, BK5*30/100/100, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="BS5" s="17">
-        <f t="shared" ref="BS5" si="5">SUM(BN5:BR5)</f>
-        <v>0.48931034482758623</v>
-      </c>
-    </row>
-    <row r="6" spans="1:80" ht="13.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="20"/>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="20"/>
+      <c r="AS5" s="20"/>
+      <c r="AT5" s="20"/>
+      <c r="AU5" s="20"/>
+      <c r="AV5" s="20"/>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="20"/>
+      <c r="BA5" s="20"/>
+      <c r="BB5" s="20"/>
+      <c r="BC5" s="20"/>
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="20"/>
+      <c r="BF5" s="20"/>
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="20"/>
+      <c r="BI5" s="19"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="20"/>
+      <c r="BL5" s="23"/>
+      <c r="BM5" s="23"/>
+      <c r="BN5" s="17"/>
+      <c r="BO5" s="17"/>
+      <c r="BP5" s="17"/>
+      <c r="BQ5" s="17"/>
+      <c r="BR5" s="17"/>
+      <c r="BS5" s="17"/>
+    </row>
+    <row r="6" spans="1:80" ht="13.8">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="20"/>
@@ -2174,10 +2012,10 @@
       <c r="BR6" s="17"/>
       <c r="BS6" s="17"/>
     </row>
-    <row r="7" spans="1:80" ht="13.2">
+    <row r="7" spans="1:80" ht="13.8">
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="21"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
@@ -2247,10 +2085,10 @@
       <c r="BR7" s="17"/>
       <c r="BS7" s="17"/>
     </row>
-    <row r="8" spans="1:80" ht="13.2">
+    <row r="8" spans="1:80" ht="13.8">
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="21"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -2393,12 +2231,12 @@
       <c r="BR9" s="17"/>
       <c r="BS9" s="17"/>
     </row>
-    <row r="10" spans="1:80" ht="13.2">
+    <row r="10" spans="1:80" ht="13.8">
       <c r="A10" s="19"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="21"/>
-      <c r="E10" s="20"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="20"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -28275,7 +28113,7 @@
     <mergeCell ref="BL1:BN2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E5" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
       <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training"</formula1>
     </dataValidation>
   </dataValidations>
